--- a/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_44.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2922289.537670172</v>
+        <v>2915422.544721516</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162897619</v>
+        <v>286.4107162897176</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162897619</v>
+        <v>286.4107162897176</v>
       </c>
     </row>
     <row r="11">
@@ -660,7 +660,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984979</v>
+        <v>39.04534712526427</v>
       </c>
       <c r="E2" t="n">
         <v>4.363289606868648</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>108.0318071824838</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>199.8180013219743</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>19.86273944538755</v>
+        <v>385</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -903,7 +903,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>33.59582009342634</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
         <v>3.75737228701621</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -982,13 +982,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>385</v>
       </c>
       <c r="Y6" t="n">
-        <v>160.4202766423893</v>
+        <v>152.9521214909335</v>
       </c>
     </row>
     <row r="7">
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
@@ -1252,22 +1252,22 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
+        <v>66.5639999646113</v>
+      </c>
+      <c r="T9" t="n">
+        <v>305.214484270644</v>
+      </c>
+      <c r="U9" t="n">
         <v>385</v>
       </c>
-      <c r="T9" t="n">
-        <v>385</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.2103597601867477</v>
-      </c>
       <c r="V9" t="n">
-        <v>174.1580567570681</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751172837</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1328,7 +1328,7 @@
         <v>240.445564079015</v>
       </c>
       <c r="P10" t="n">
-        <v>287.4478973282775</v>
+        <v>285.856726682227</v>
       </c>
       <c r="Q10" t="n">
         <v>325.839266425598</v>
@@ -1368,7 +1368,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>99.47457824299391</v>
+        <v>103.4399696284084</v>
       </c>
       <c r="D11" t="n">
         <v>60.33915573984979</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>144.8481678023229</v>
@@ -1450,19 +1450,19 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T12" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U12" t="n">
         <v>50.21035976018675</v>
@@ -1653,13 +1653,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T14" t="n">
         <v>236.6755817285639</v>
       </c>
       <c r="U14" t="n">
-        <v>303.1866879340253</v>
+        <v>299.2212965486107</v>
       </c>
       <c r="V14" t="n">
         <v>279.8510241668239</v>
@@ -1696,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>325.7395358750273</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H15" t="n">
-        <v>86.93822665041519</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T17" t="n">
         <v>236.6755817285639</v>
@@ -1902,7 +1902,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>288.3734759809475</v>
+        <v>292.3388673663621</v>
       </c>
       <c r="X17" t="n">
         <v>242.2818334606677</v>
@@ -1933,13 +1933,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V18" t="n">
-        <v>260.0620438256142</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>82.37314290982852</v>
@@ -2082,7 +2082,7 @@
         <v>99.47457824299391</v>
       </c>
       <c r="D20" t="n">
-        <v>64.30454712526431</v>
+        <v>60.33915573984979</v>
       </c>
       <c r="E20" t="n">
         <v>54.36328960686865</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S20" t="n">
         <v>144.8481678023229</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2200,10 +2200,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>62.67776252544228</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>547.2737972923793</v>
+        <v>270.3153174799449</v>
       </c>
       <c r="S21" t="n">
         <v>116.5639999646113</v>
@@ -2319,7 +2319,7 @@
         <v>99.47457824299391</v>
       </c>
       <c r="D23" t="n">
-        <v>64.30454712526431</v>
+        <v>60.33915573984979</v>
       </c>
       <c r="E23" t="n">
         <v>54.36328960686865</v>
@@ -2331,7 +2331,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>197.2737972923793</v>
@@ -2449,7 +2449,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U24" t="n">
-        <v>50.21035976018675</v>
+        <v>289.8088571951495</v>
       </c>
       <c r="V24" t="n">
         <v>64.51066719152016</v>
@@ -2461,7 +2461,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>119.3970580696643</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2571,7 +2571,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>144.8481678023229</v>
@@ -2644,13 +2644,13 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>86.93822665041519</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2689,10 +2689,10 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V27" t="n">
-        <v>64.51066719152016</v>
+        <v>127.1884297169626</v>
       </c>
       <c r="W27" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X27" t="n">
         <v>69.86273944538755</v>
@@ -2790,13 +2790,13 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>99.47457824299391</v>
+        <v>103.4399696284084</v>
       </c>
       <c r="D29" t="n">
         <v>60.33915573984979</v>
       </c>
       <c r="E29" t="n">
-        <v>58.32868099228319</v>
+        <v>54.36328960686865</v>
       </c>
       <c r="F29" t="n">
         <v>54.88962870801186</v>
@@ -2869,10 +2869,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>262.0138729201192</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S30" t="n">
         <v>116.5639999646113</v>
@@ -2923,7 +2923,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U30" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856293</v>
       </c>
       <c r="V30" t="n">
         <v>64.51066719152016</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>144.8481678023229</v>
@@ -3087,7 +3087,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>288.3734759809475</v>
+        <v>292.3388673663621</v>
       </c>
       <c r="X32" t="n">
         <v>242.2818334606677</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3154,7 +3154,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S33" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T33" t="n">
         <v>55.35776521751382</v>
@@ -3166,13 +3166,13 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>432.3731429098285</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X33" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>112.0691552915768</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="34">
@@ -3349,13 +3349,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>70.00566530352985</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>197.2737972923793</v>
@@ -3397,7 +3397,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
-        <v>50.21035976018675</v>
+        <v>137.148586410602</v>
       </c>
       <c r="V36" t="n">
         <v>64.51066719152016</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T38" t="n">
         <v>236.6755817285639</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34.55655664632661</v>
+        <v>121.4947832967418</v>
       </c>
       <c r="C39" t="n">
         <v>11.09991244551929</v>
@@ -3592,13 +3592,13 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>392.8251739264733</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3829,13 +3829,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>136.3296194165495</v>
       </c>
     </row>
     <row r="43">
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
@@ -4099,16 +4099,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T45" t="n">
         <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>112.8881222856293</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
         <v>64.51066719152016</v>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D2" t="n">
         <v>52.03227202568092</v>
@@ -4330,16 +4330,16 @@
         <v>30.8</v>
       </c>
       <c r="M2" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="N2" t="n">
-        <v>396.55</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>777.6999999999999</v>
+        <v>1174.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4348,25 +4348,25 @@
         <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>897.189519579215</v>
+        <v>139.9230375580644</v>
       </c>
       <c r="C3" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="D3" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="E3" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="F3" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="G3" t="n">
-        <v>568.1596853620156</v>
+        <v>30.8</v>
       </c>
       <c r="H3" t="n">
-        <v>232.6363649716912</v>
+        <v>30.8</v>
       </c>
       <c r="I3" t="n">
         <v>30.8</v>
@@ -4442,10 +4442,10 @@
         <v>917.2528927563742</v>
       </c>
       <c r="X3" t="n">
-        <v>897.189519579215</v>
+        <v>528.3640038674853</v>
       </c>
       <c r="Y3" t="n">
-        <v>897.189519579215</v>
+        <v>528.3640038674853</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>492.0614845891717</v>
+        <v>1022.260933153428</v>
       </c>
       <c r="C4" t="n">
-        <v>618.0634904076074</v>
+        <v>1148.262938971864</v>
       </c>
       <c r="D4" t="n">
-        <v>731.3826345326075</v>
+        <v>1261.582083096864</v>
       </c>
       <c r="E4" t="n">
-        <v>849.2115387440206</v>
+        <v>1379.410987308277</v>
       </c>
       <c r="F4" t="n">
-        <v>957.7833804114658</v>
+        <v>1386.593434113115</v>
       </c>
       <c r="G4" t="n">
-        <v>957.7833804114658</v>
+        <v>1540</v>
       </c>
       <c r="H4" t="n">
-        <v>957.7833804114658</v>
+        <v>1540</v>
       </c>
       <c r="I4" t="n">
-        <v>1178.916259347549</v>
+        <v>1540</v>
       </c>
       <c r="J4" t="n">
         <v>1540</v>
@@ -4485,22 +4485,22 @@
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
@@ -4512,19 +4512,19 @@
         <v>30.8</v>
       </c>
       <c r="U4" t="n">
-        <v>30.8</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="V4" t="n">
-        <v>229.621392885946</v>
+        <v>476.1725855242326</v>
       </c>
       <c r="W4" t="n">
-        <v>229.621392885946</v>
+        <v>648.0635037839101</v>
       </c>
       <c r="X4" t="n">
-        <v>380.6521839101395</v>
+        <v>799.0942948081035</v>
       </c>
       <c r="Y4" t="n">
-        <v>492.0614845891717</v>
+        <v>910.5035954871358</v>
       </c>
     </row>
     <row r="5">
@@ -4546,37 +4546,37 @@
         <v>76.62106170097975</v>
       </c>
       <c r="F5" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G5" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H5" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I5" t="n">
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>396.55</v>
+        <v>30.8</v>
       </c>
       <c r="K5" t="n">
-        <v>396.55</v>
+        <v>30.8</v>
       </c>
       <c r="L5" t="n">
-        <v>777.6999999999999</v>
+        <v>30.8</v>
       </c>
       <c r="M5" t="n">
-        <v>1158.85</v>
+        <v>411.9500000000026</v>
       </c>
       <c r="N5" t="n">
-        <v>1540</v>
+        <v>793.1000000000051</v>
       </c>
       <c r="O5" t="n">
-        <v>1540</v>
+        <v>1174.250000000007</v>
       </c>
       <c r="P5" t="n">
-        <v>1540</v>
+        <v>1174.250000000007</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>366.3233203903244</v>
+        <v>373.8669114524009</v>
       </c>
       <c r="C6" t="n">
-        <v>366.3233203903244</v>
+        <v>373.8669114524009</v>
       </c>
       <c r="D6" t="n">
-        <v>366.3233203903244</v>
+        <v>373.8669114524009</v>
       </c>
       <c r="E6" t="n">
-        <v>366.3233203903244</v>
+        <v>373.8669114524009</v>
       </c>
       <c r="F6" t="n">
-        <v>366.3233203903244</v>
+        <v>30.8</v>
       </c>
       <c r="G6" t="n">
-        <v>366.3233203903244</v>
+        <v>30.8</v>
       </c>
       <c r="H6" t="n">
         <v>30.8</v>
@@ -4682,7 +4682,7 @@
         <v>528.3640038674853</v>
       </c>
       <c r="Y6" t="n">
-        <v>366.3233203903244</v>
+        <v>373.8669114524009</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1001.035674768119</v>
+        <v>404.0685093339813</v>
       </c>
       <c r="C7" t="n">
-        <v>1127.037680586555</v>
+        <v>530.0705151524171</v>
       </c>
       <c r="D7" t="n">
-        <v>1240.356824711555</v>
+        <v>643.3896592774172</v>
       </c>
       <c r="E7" t="n">
-        <v>1358.185728922968</v>
+        <v>761.2185634888302</v>
       </c>
       <c r="F7" t="n">
-        <v>1370.483414840602</v>
+        <v>885.5795360807657</v>
       </c>
       <c r="G7" t="n">
-        <v>1370.483414840602</v>
+        <v>1038.986101967651</v>
       </c>
       <c r="H7" t="n">
-        <v>1540</v>
+        <v>1208.502687127049</v>
       </c>
       <c r="I7" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="J7" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
       </c>
       <c r="L7" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M7" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N7" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O7" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P7" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q7" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T7" t="n">
-        <v>256.125934252978</v>
+        <v>30.8</v>
       </c>
       <c r="U7" t="n">
-        <v>256.125934252978</v>
+        <v>30.8</v>
       </c>
       <c r="V7" t="n">
-        <v>454.9473271389239</v>
+        <v>30.79999999999222</v>
       </c>
       <c r="W7" t="n">
-        <v>626.8382453986013</v>
+        <v>30.79999999999222</v>
       </c>
       <c r="X7" t="n">
-        <v>777.8690364227948</v>
+        <v>180.9018709886569</v>
       </c>
       <c r="Y7" t="n">
-        <v>889.2783371018271</v>
+        <v>292.3111716676892</v>
       </c>
     </row>
     <row r="8">
@@ -4771,49 +4771,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C8" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D8" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E8" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F8" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>411.95</v>
+        <v>411.9500000000015</v>
       </c>
       <c r="K8" t="n">
-        <v>411.95</v>
+        <v>411.9500000000015</v>
       </c>
       <c r="L8" t="n">
-        <v>411.95</v>
+        <v>411.9500000000015</v>
       </c>
       <c r="M8" t="n">
-        <v>793.1</v>
+        <v>793.1000000000043</v>
       </c>
       <c r="N8" t="n">
-        <v>1174.25</v>
+        <v>1174.250000000007</v>
       </c>
       <c r="O8" t="n">
-        <v>1540</v>
+        <v>1174.250000000007</v>
       </c>
       <c r="P8" t="n">
-        <v>1540</v>
+        <v>1174.250000000007</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
@@ -4822,25 +4822,25 @@
         <v>1540</v>
       </c>
       <c r="S8" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X8" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4895,19 +4895,19 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1037.471008962092</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S9" t="n">
-        <v>648.582120073203</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T9" t="n">
-        <v>259.6932311843141</v>
+        <v>487.1096460068043</v>
       </c>
       <c r="U9" t="n">
-        <v>259.4807465780648</v>
+        <v>98.22075711791538</v>
       </c>
       <c r="V9" t="n">
         <v>83.56351753052128</v>
@@ -4929,46 +4929,46 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>674.568045150942</v>
+        <v>1247.586867406406</v>
       </c>
       <c r="C10" t="n">
-        <v>674.568045150942</v>
+        <v>1373.588873224842</v>
       </c>
       <c r="D10" t="n">
-        <v>674.568045150942</v>
+        <v>1486.908017349842</v>
       </c>
       <c r="E10" t="n">
-        <v>792.396949362355</v>
+        <v>1540.000000000005</v>
       </c>
       <c r="F10" t="n">
-        <v>792.396949362355</v>
+        <v>1540.000000000005</v>
       </c>
       <c r="G10" t="n">
-        <v>792.396949362355</v>
+        <v>1540.000000000005</v>
       </c>
       <c r="H10" t="n">
-        <v>961.9135345217526</v>
+        <v>1540.000000000005</v>
       </c>
       <c r="I10" t="n">
-        <v>1068.551825410686</v>
+        <v>1540.000000000005</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063137</v>
+        <v>1540.000000000005</v>
       </c>
       <c r="K10" t="n">
         <v>1540.000000000005</v>
       </c>
       <c r="L10" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012349</v>
       </c>
       <c r="M10" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484521</v>
       </c>
       <c r="N10" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038375</v>
       </c>
       <c r="O10" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878547</v>
       </c>
       <c r="P10" t="n">
         <v>689.8317115219688</v>
@@ -4989,16 +4989,16 @@
         <v>502.6771268912646</v>
       </c>
       <c r="V10" t="n">
-        <v>502.6771268912646</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="W10" t="n">
-        <v>674.568045150942</v>
+        <v>873.3894380368879</v>
       </c>
       <c r="X10" t="n">
-        <v>674.568045150942</v>
+        <v>1024.420229061081</v>
       </c>
       <c r="Y10" t="n">
-        <v>674.568045150942</v>
+        <v>1135.829529740114</v>
       </c>
     </row>
     <row r="11">
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C11" t="n">
         <v>328.9211162073474</v>
@@ -5038,13 +5038,13 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M11" t="n">
-        <v>1243.990904947333</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N11" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O11" t="n">
         <v>1797.400904947332</v>
@@ -5056,28 +5056,28 @@
         <v>2236</v>
       </c>
       <c r="R11" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S11" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X11" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y11" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C12" t="n">
-        <v>461.5662247731743</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D12" t="n">
-        <v>387.7869114524009</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E12" t="n">
-        <v>387.7869114524009</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F12" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="G12" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="H12" t="n">
         <v>44.72</v>
@@ -5141,22 +5141,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T12" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U12" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V12" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W12" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X12" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y12" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="13">
@@ -5272,22 +5272,22 @@
         <v>44.72</v>
       </c>
       <c r="K14" t="n">
-        <v>179.7320762183976</v>
+        <v>44.72</v>
       </c>
       <c r="L14" t="n">
-        <v>733.1420762183976</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="M14" t="n">
-        <v>1243.990904947333</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N14" t="n">
-        <v>1797.400904947332</v>
+        <v>1129.18</v>
       </c>
       <c r="O14" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P14" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5296,10 +5296,10 @@
         <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T14" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U14" t="n">
         <v>1544.373295489988</v>
@@ -5339,7 +5339,7 @@
         <v>461.5662247731743</v>
       </c>
       <c r="G15" t="n">
-        <v>132.5363905559749</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H15" t="n">
         <v>44.72</v>
@@ -5506,25 +5506,25 @@
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M17" t="n">
-        <v>137.1709049473327</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N17" t="n">
-        <v>690.5809049473327</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O17" t="n">
-        <v>1243.990904947333</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P17" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5533,16 +5533,16 @@
         <v>2236</v>
       </c>
       <c r="S17" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T17" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V17" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W17" t="n">
         <v>970.4091539265823</v>
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>275.2516144816847</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C18" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D18" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E18" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F18" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G18" t="n">
-        <v>264.0395817084329</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I18" t="n">
         <v>44.72</v>
@@ -5621,16 +5621,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V18" t="n">
-        <v>513.8211415197422</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W18" t="n">
-        <v>430.6159466613296</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X18" t="n">
-        <v>360.0475229791199</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y18" t="n">
-        <v>310.1572272557519</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="19">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C19" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D19" t="n">
         <v>1010.366979583462</v>
@@ -5700,16 +5700,16 @@
         <v>380.3468717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X19" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="20">
@@ -5719,10 +5719,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C20" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D20" t="n">
         <v>267.972474045883</v>
@@ -5743,52 +5743,52 @@
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>436.0291130376557</v>
+        <v>137.1709049473328</v>
       </c>
       <c r="K20" t="n">
-        <v>575.7700000000003</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L20" t="n">
-        <v>575.7700000000003</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M20" t="n">
-        <v>575.7700000000003</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N20" t="n">
-        <v>1129.18</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O20" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S20" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T20" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U20" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V20" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W20" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X20" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y20" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="21">
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.93203277325181</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C21" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D21" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E21" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F21" t="n">
         <v>44.72</v>
@@ -5843,31 +5843,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1136.841549130715</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>584.0397336838671</v>
+        <v>927.106645136268</v>
       </c>
       <c r="S21" t="n">
-        <v>466.2983195781991</v>
+        <v>809.3652310305999</v>
       </c>
       <c r="T21" t="n">
-        <v>410.3813850150538</v>
+        <v>753.4482964674547</v>
       </c>
       <c r="U21" t="n">
-        <v>359.6638499037541</v>
+        <v>702.730761356155</v>
       </c>
       <c r="V21" t="n">
-        <v>294.5015598113094</v>
+        <v>637.5684712637103</v>
       </c>
       <c r="W21" t="n">
-        <v>211.2963649528968</v>
+        <v>554.3632764052976</v>
       </c>
       <c r="X21" t="n">
-        <v>140.7279412706871</v>
+        <v>483.794852723088</v>
       </c>
       <c r="Y21" t="n">
-        <v>90.8376455473191</v>
+        <v>433.9045569997199</v>
       </c>
     </row>
     <row r="22">
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C22" t="n">
         <v>946.5478354584615</v>
@@ -5943,10 +5943,10 @@
         <v>652.0591829427149</v>
       </c>
       <c r="X22" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y22" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="23">
@@ -5962,16 +5962,16 @@
         <v>332.9265620512004</v>
       </c>
       <c r="D23" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E23" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F23" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
         <v>44.72</v>
@@ -5980,22 +5980,22 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1151.54</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>1151.54</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N23" t="n">
-        <v>1151.54</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O23" t="n">
-        <v>1682.59</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P23" t="n">
         <v>2236</v>
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>402.0654643105373</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C24" t="n">
-        <v>390.8534315372855</v>
+        <v>44.72</v>
       </c>
       <c r="D24" t="n">
-        <v>390.8534315372855</v>
+        <v>44.72</v>
       </c>
       <c r="E24" t="n">
         <v>44.72</v>
@@ -6080,31 +6080,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R24" t="n">
-        <v>1000.885958457041</v>
+        <v>826.0584179616072</v>
       </c>
       <c r="S24" t="n">
-        <v>883.1445443513733</v>
+        <v>708.3170038559392</v>
       </c>
       <c r="T24" t="n">
-        <v>827.2276097882281</v>
+        <v>652.400069292794</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V24" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X24" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y24" t="n">
-        <v>436.9710770846045</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="25">
@@ -6171,7 +6171,7 @@
         <v>183.2956791588049</v>
       </c>
       <c r="U25" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V25" t="n">
         <v>521.9574820108303</v>
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C26" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D26" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E26" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F26" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G26" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H26" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I26" t="n">
         <v>44.72</v>
@@ -6229,10 +6229,10 @@
         <v>946.8779417665908</v>
       </c>
       <c r="N26" t="n">
-        <v>1500.287941766591</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="O26" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P26" t="n">
         <v>1797.400904947332</v>
@@ -6241,28 +6241,28 @@
         <v>2236</v>
       </c>
       <c r="R26" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S26" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T26" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U26" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V26" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W26" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X26" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y26" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="27">
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C27" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D27" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E27" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F27" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G27" t="n">
-        <v>132.5363905559749</v>
+        <v>44.72</v>
       </c>
       <c r="H27" t="n">
-        <v>132.5363905559749</v>
+        <v>44.72</v>
       </c>
       <c r="I27" t="n">
         <v>44.72</v>
@@ -6332,16 +6332,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V27" t="n">
-        <v>711.3477845844836</v>
+        <v>648.036913346663</v>
       </c>
       <c r="W27" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X27" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y27" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="28">
@@ -6433,10 +6433,10 @@
         <v>433.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D29" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E29" t="n">
         <v>213.0600603015712</v>
@@ -6454,22 +6454,22 @@
         <v>44.72</v>
       </c>
       <c r="J29" t="n">
-        <v>44.72</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="K29" t="n">
-        <v>44.72</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L29" t="n">
-        <v>44.72</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M29" t="n">
-        <v>555.568828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N29" t="n">
-        <v>690.5809049473327</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O29" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P29" t="n">
         <v>1797.400904947332</v>
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>407.3842417608302</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C30" t="n">
-        <v>396.1722089875784</v>
+        <v>44.72</v>
       </c>
       <c r="D30" t="n">
         <v>44.72</v>
@@ -6557,28 +6557,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>935.4919426714454</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S30" t="n">
-        <v>817.7505285657774</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T30" t="n">
-        <v>761.8335940026321</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U30" t="n">
-        <v>711.1160588913324</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V30" t="n">
-        <v>645.9537687988877</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W30" t="n">
-        <v>562.7485739404751</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X30" t="n">
-        <v>492.1801502582655</v>
+        <v>494.2632948060406</v>
       </c>
       <c r="Y30" t="n">
-        <v>442.2898545348975</v>
+        <v>444.3729990826726</v>
       </c>
     </row>
     <row r="31">
@@ -6694,40 +6694,40 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M32" t="n">
-        <v>1243.990904947333</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N32" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>1243.990904947333</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P32" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
       </c>
       <c r="R32" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S32" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T32" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U32" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V32" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W32" t="n">
         <v>970.4091539265823</v>
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C33" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D33" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E33" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F33" t="n">
         <v>44.72</v>
@@ -6797,16 +6797,16 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S33" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T33" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U33" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V33" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W33" t="n">
         <v>274.6072361907174</v>
@@ -6815,7 +6815,7 @@
         <v>204.0388125085078</v>
       </c>
       <c r="Y33" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="34">
@@ -6879,10 +6879,10 @@
         <v>44.72</v>
       </c>
       <c r="T34" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U34" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V34" t="n">
         <v>521.9574820108303</v>
@@ -6931,22 +6931,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L35" t="n">
-        <v>989.4391130376558</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M35" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N35" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,19 +6983,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>402.0654643105373</v>
+        <v>384.9618669904511</v>
       </c>
       <c r="C36" t="n">
-        <v>390.8534315372855</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="D36" t="n">
-        <v>390.8534315372855</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E36" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F36" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G36" t="n">
         <v>44.72</v>
@@ -7028,31 +7028,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>1129.439627132647</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>930.1731652211525</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>812.4317511154845</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T36" t="n">
-        <v>756.5148165523393</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U36" t="n">
-        <v>705.7972814410396</v>
+        <v>688.6936841209533</v>
       </c>
       <c r="V36" t="n">
-        <v>640.6349913485949</v>
+        <v>623.5313940285087</v>
       </c>
       <c r="W36" t="n">
-        <v>557.4297964901822</v>
+        <v>540.3261991700961</v>
       </c>
       <c r="X36" t="n">
-        <v>486.8613728079725</v>
+        <v>469.7577754878864</v>
       </c>
       <c r="Y36" t="n">
-        <v>436.9710770846045</v>
+        <v>419.8674797645184</v>
       </c>
     </row>
     <row r="37">
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F37" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G37" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H37" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I37" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J37" t="n">
         <v>1860.696627021627</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7165,22 +7165,22 @@
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>179.7320762183977</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>179.7320762183977</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>179.7320762183977</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M38" t="n">
-        <v>690.5809049473327</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N38" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O38" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P38" t="n">
         <v>1797.400904947332</v>
@@ -7189,7 +7189,7 @@
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
         <v>2085.68327354774</v>
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>275.2516144816847</v>
+        <v>384.9618669904511</v>
       </c>
       <c r="C39" t="n">
-        <v>264.0395817084329</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="D39" t="n">
-        <v>264.0395817084329</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E39" t="n">
-        <v>264.0395817084329</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F39" t="n">
-        <v>264.0395817084329</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G39" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>803.3593153922999</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>685.6179012866319</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>629.7009667234867</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U39" t="n">
-        <v>578.9834316121869</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V39" t="n">
-        <v>513.8211415197422</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>430.6159466613296</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X39" t="n">
-        <v>360.0475229791199</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y39" t="n">
-        <v>310.1572272557519</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="40">
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7378,25 +7378,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G41" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
@@ -7405,19 +7405,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>989.4391130376558</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M41" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N41" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P41" t="n">
         <v>1797.400904947332</v>
@@ -7426,28 +7426,28 @@
         <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>119.2429040110725</v>
+        <v>384.9618669904511</v>
       </c>
       <c r="C42" t="n">
-        <v>108.0308712378207</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="D42" t="n">
-        <v>108.0308712378207</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E42" t="n">
-        <v>108.0308712378207</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F42" t="n">
-        <v>108.0308712378207</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G42" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="H42" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="I42" t="n">
         <v>44.72</v>
@@ -7526,7 +7526,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>154.1485167851398</v>
+        <v>419.8674797645184</v>
       </c>
     </row>
     <row r="43">
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
@@ -7642,49 +7642,49 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>575.7700000000003</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L44" t="n">
-        <v>575.7700000000003</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M44" t="n">
-        <v>575.7700000000003</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="N44" t="n">
-        <v>1129.18</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O44" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7742,28 +7742,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T45" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U45" t="n">
-        <v>713.1992034391076</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V45" t="n">
-        <v>648.0369133466629</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W45" t="n">
-        <v>564.8317184882503</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X45" t="n">
-        <v>494.2632948060407</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>444.3729990826727</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7827,7 +7827,7 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U46" t="n">
         <v>372.6360891248843</v>
@@ -7973,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>913.7065720867618</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O2" t="n">
         <v>455.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>385.2870600406814</v>
+        <v>369.7315044851259</v>
       </c>
       <c r="Q2" t="n">
-        <v>557.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>404.4874506895348</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>929.2621276423173</v>
+        <v>929.2621276423199</v>
       </c>
       <c r="N5" t="n">
-        <v>862.2489580698352</v>
+        <v>862.2489580698377</v>
       </c>
       <c r="O5" t="n">
-        <v>70.24786957409245</v>
+        <v>455.2478695740942</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.8226843274854</v>
+        <v>542.267128771923</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450903</v>
+        <v>420.0430062450919</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8447,19 +8447,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>929.2621276423173</v>
+        <v>929.2621276423201</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698352</v>
+        <v>862.248958069838</v>
       </c>
       <c r="O8" t="n">
-        <v>439.6923140185369</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>172.8226843274854</v>
+        <v>542.2671287719228</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8681,16 +8681,16 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>629.2478695740924</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
@@ -8915,25 +8915,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>559</v>
+        <v>536.4141414141418</v>
       </c>
       <c r="M14" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N14" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,7 +9149,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -9158,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>637.6468801143706</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
         <v>1036.248958069835</v>
@@ -9167,10 +9167,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,13 +9386,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>128.4277587171436</v>
       </c>
       <c r="K20" t="n">
-        <v>141.1524110730754</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
         <v>544.2621276423173</v>
@@ -9401,13 +9401,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>606.6620109882339</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>559.2870600406815</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q23" t="n">
         <v>172.8226843274854</v>
@@ -9872,13 +9872,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>370.361973797064</v>
       </c>
       <c r="P26" t="n">
-        <v>300.4011642636528</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,10 +10097,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>35.04300624509033</v>
+        <v>171.4188408091283</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10109,13 +10109,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>613.6247926338732</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10337,25 +10337,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>801.385149773304</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P32" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,25 +10574,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>801.3851497733039</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>254.3913627391524</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,7 +10808,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>171.4188408091284</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -10823,10 +10823,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P38" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11048,13 +11048,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
         <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>801.3851497733039</v>
       </c>
       <c r="N41" t="n">
         <v>477.2489580698352</v>
@@ -11063,7 +11063,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11285,7 +11285,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>141.1524110730754</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -11294,16 +11294,16 @@
         <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>734.3719802008219</v>
       </c>
       <c r="O44" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P44" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646050784</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23186,7 +23186,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.591170646050386</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -26281,7 +26281,7 @@
         <v>1385314.744365854</v>
       </c>
       <c r="F2" t="n">
-        <v>1385314.744365854</v>
+        <v>1385314.744365853</v>
       </c>
       <c r="G2" t="n">
         <v>1385314.744365853</v>
@@ -26296,7 +26296,7 @@
         <v>1385314.744365854</v>
       </c>
       <c r="K2" t="n">
-        <v>1385314.744365854</v>
+        <v>1385314.744365853</v>
       </c>
       <c r="L2" t="n">
         <v>1385314.744365854</v>
@@ -26305,7 +26305,7 @@
         <v>1385314.744365854</v>
       </c>
       <c r="N2" t="n">
-        <v>1385314.744365854</v>
+        <v>1385314.744365853</v>
       </c>
       <c r="O2" t="n">
         <v>1385314.744365854</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114471</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380801</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984991</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>621803.012561289</v>
+        <v>620287.156872973</v>
       </c>
       <c r="C6" t="n">
-        <v>759380.9926951031</v>
+        <v>757865.137006787</v>
       </c>
       <c r="D6" t="n">
-        <v>761441.7646074191</v>
+        <v>759925.9089191031</v>
       </c>
       <c r="E6" t="n">
-        <v>437561.3411393185</v>
+        <v>435819.4913262109</v>
       </c>
       <c r="F6" t="n">
-        <v>780752.2364848227</v>
+        <v>779010.3866717148</v>
       </c>
       <c r="G6" t="n">
-        <v>782697.812953008</v>
+        <v>780955.9631399005</v>
       </c>
       <c r="H6" t="n">
-        <v>784646.0897703095</v>
+        <v>782904.2399572019</v>
       </c>
       <c r="I6" t="n">
-        <v>786597.0864136697</v>
+        <v>784855.2366005621</v>
       </c>
       <c r="J6" t="n">
-        <v>373030.8226152951</v>
+        <v>371288.9728021872</v>
       </c>
       <c r="K6" t="n">
-        <v>790507.3183675145</v>
+        <v>788765.4685544062</v>
       </c>
       <c r="L6" t="n">
-        <v>792466.5939277736</v>
+        <v>790724.744114666</v>
       </c>
       <c r="M6" t="n">
-        <v>733180.6698237531</v>
+        <v>731438.8200106454</v>
       </c>
       <c r="N6" t="n">
-        <v>796393.5668586065</v>
+        <v>794651.7170454985</v>
       </c>
       <c r="O6" t="n">
-        <v>518361.3061163449</v>
+        <v>516619.4563032371</v>
       </c>
       <c r="P6" t="n">
-        <v>800331.9089673547</v>
+        <v>798590.0591542471</v>
       </c>
     </row>
   </sheetData>
@@ -26984,16 +26984,16 @@
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>350</v>
@@ -27005,7 +27005,7 @@
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -27036,10 +27036,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
@@ -27079,7 +27079,7 @@
         <v>385</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27088,13 +27088,13 @@
         <v>174</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -27106,13 +27106,13 @@
         <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27439,7 +27439,7 @@
         <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="E2" t="n">
         <v>400</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27512,10 +27512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>253.0681052630355</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>17.30838456937427</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27578,7 +27578,7 @@
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>400</v>
+        <v>34.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
@@ -27603,19 +27603,19 @@
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>384.0513829045553</v>
+        <v>281.6378527403056</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
         <v>288.520773801143</v>
@@ -27648,13 +27648,13 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
@@ -27682,7 +27682,7 @@
         <v>400</v>
       </c>
       <c r="F5" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27761,13 +27761,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27818,7 +27818,7 @@
         <v>34.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>238.9711161237451</v>
+        <v>246.4392712752008</v>
       </c>
     </row>
     <row r="7">
@@ -27840,22 +27840,22 @@
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>286.8047609350494</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,22 +27879,22 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162083</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>399.0616969338093</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -28031,22 +28031,22 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>81.5639999646113</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>20.35776521751382</v>
+        <v>100.1432809468698</v>
       </c>
       <c r="U9" t="n">
+        <v>15.21035976018675</v>
+      </c>
+      <c r="V9" t="n">
         <v>400</v>
-      </c>
-      <c r="V9" t="n">
-        <v>240.352610434452</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28065,16 +28065,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>334.6091701401521</v>
       </c>
       <c r="F10" t="n">
         <v>274.3828559677419</v>
@@ -28083,16 +28083,16 @@
         <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
-        <v>284.3489009624748</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28125,16 +28125,16 @@
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28147,7 +28147,7 @@
         <v>350</v>
       </c>
       <c r="C11" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="D11" t="n">
         <v>350</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
         <v>350</v>
@@ -28229,19 +28229,19 @@
         <v>350</v>
       </c>
       <c r="D12" t="n">
-        <v>274.8961667101369</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
-        <v>332.1680871864211</v>
+        <v>269.4903246609787</v>
       </c>
       <c r="I12" t="n">
         <v>217.1263858913485</v>
@@ -28277,7 +28277,7 @@
         <v>350</v>
       </c>
       <c r="T12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>350</v>
@@ -28432,13 +28432,13 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T14" t="n">
         <v>350</v>
       </c>
       <c r="U14" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="V14" t="n">
         <v>350</v>
@@ -28475,10 +28475,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H15" t="n">
-        <v>245.2298605360059</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>217.1263858913485</v>
@@ -28669,7 +28669,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T17" t="n">
         <v>350</v>
@@ -28681,7 +28681,7 @@
         <v>350</v>
       </c>
       <c r="W17" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="X17" t="n">
         <v>350</v>
@@ -28712,13 +28712,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>325.7395358750273</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H18" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28757,7 +28757,7 @@
         <v>350</v>
       </c>
       <c r="V18" t="n">
-        <v>154.448623365906</v>
+        <v>350</v>
       </c>
       <c r="W18" t="n">
         <v>350</v>
@@ -28782,7 +28782,7 @@
         <v>350</v>
       </c>
       <c r="D19" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E19" t="n">
         <v>350</v>
@@ -28836,7 +28836,7 @@
         <v>350</v>
       </c>
       <c r="V19" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W19" t="n">
         <v>350</v>
@@ -28861,7 +28861,7 @@
         <v>350</v>
       </c>
       <c r="D20" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="E20" t="n">
         <v>350</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S20" t="n">
         <v>350</v>
@@ -28946,7 +28946,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>325.7395358750273</v>
@@ -28979,10 +28979,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>110.4015025650373</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>276.9584798124344</v>
       </c>
       <c r="S21" t="n">
         <v>350</v>
@@ -29016,7 +29016,7 @@
         <v>350</v>
       </c>
       <c r="C22" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="D22" t="n">
         <v>350</v>
@@ -29079,7 +29079,7 @@
         <v>350</v>
       </c>
       <c r="X22" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="Y22" t="n">
         <v>350</v>
@@ -29098,19 +29098,19 @@
         <v>350</v>
       </c>
       <c r="D23" t="n">
+        <v>350</v>
+      </c>
+      <c r="E23" t="n">
+        <v>350</v>
+      </c>
+      <c r="F23" t="n">
+        <v>350</v>
+      </c>
+      <c r="G23" t="n">
+        <v>350</v>
+      </c>
+      <c r="H23" t="n">
         <v>346.0346086145855</v>
-      </c>
-      <c r="E23" t="n">
-        <v>350</v>
-      </c>
-      <c r="F23" t="n">
-        <v>350</v>
-      </c>
-      <c r="G23" t="n">
-        <v>350</v>
-      </c>
-      <c r="H23" t="n">
-        <v>350</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29180,7 +29180,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>350</v>
@@ -29228,7 +29228,7 @@
         <v>350</v>
       </c>
       <c r="U24" t="n">
-        <v>350</v>
+        <v>110.4015025650372</v>
       </c>
       <c r="V24" t="n">
         <v>350</v>
@@ -29240,7 +29240,7 @@
         <v>350</v>
       </c>
       <c r="Y24" t="n">
-        <v>279.99433469647</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25">
@@ -29307,10 +29307,10 @@
         <v>350</v>
       </c>
       <c r="U25" t="n">
+        <v>350</v>
+      </c>
+      <c r="V25" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="V25" t="n">
-        <v>350</v>
       </c>
       <c r="W25" t="n">
         <v>350</v>
@@ -29350,7 +29350,7 @@
         <v>350</v>
       </c>
       <c r="I26" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
         <v>350</v>
@@ -29423,13 +29423,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H27" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I27" t="n">
-        <v>130.1881592409333</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29468,10 +29468,10 @@
         <v>350</v>
       </c>
       <c r="V27" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="W27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>350</v>
@@ -29569,13 +29569,13 @@
         <v>350</v>
       </c>
       <c r="C29" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="D29" t="n">
         <v>350</v>
       </c>
       <c r="E29" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="F29" t="n">
         <v>350</v>
@@ -29648,10 +29648,10 @@
         <v>350</v>
       </c>
       <c r="C30" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
@@ -29693,7 +29693,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
-        <v>285.25992437226</v>
+        <v>350</v>
       </c>
       <c r="S30" t="n">
         <v>350</v>
@@ -29702,7 +29702,7 @@
         <v>350</v>
       </c>
       <c r="U30" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="V30" t="n">
         <v>350</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
         <v>350</v>
@@ -29866,7 +29866,7 @@
         <v>350</v>
       </c>
       <c r="W32" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="X32" t="n">
         <v>350</v>
@@ -29894,7 +29894,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>276.9584798124345</v>
       </c>
       <c r="G33" t="n">
         <v>325.7395358750273</v>
@@ -29933,7 +29933,7 @@
         <v>350</v>
       </c>
       <c r="S33" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>350</v>
@@ -29945,13 +29945,13 @@
         <v>350</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="X33" t="n">
         <v>350</v>
       </c>
       <c r="Y33" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34">
@@ -30015,13 +30015,13 @@
         <v>350</v>
       </c>
       <c r="T34" t="n">
+        <v>350</v>
+      </c>
+      <c r="U34" t="n">
+        <v>350</v>
+      </c>
+      <c r="V34" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="U34" t="n">
-        <v>350</v>
-      </c>
-      <c r="V34" t="n">
-        <v>350</v>
       </c>
       <c r="W34" t="n">
         <v>350</v>
@@ -30128,13 +30128,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>332.1680871864211</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>103.0735997869497</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
         <v>350</v>
@@ -30176,7 +30176,7 @@
         <v>350</v>
       </c>
       <c r="U36" t="n">
-        <v>350</v>
+        <v>263.0617733495848</v>
       </c>
       <c r="V36" t="n">
         <v>350</v>
@@ -30222,7 +30222,7 @@
         <v>350</v>
       </c>
       <c r="J37" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30325,10 +30325,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T38" t="n">
         <v>350</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>350</v>
+        <v>263.0617733495848</v>
       </c>
       <c r="C39" t="n">
         <v>350</v>
@@ -30371,13 +30371,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30404,7 +30404,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>154.448623365906</v>
+        <v>350</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30435,61 +30435,61 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>350</v>
+      </c>
+      <c r="C40" t="n">
+        <v>350</v>
+      </c>
+      <c r="D40" t="n">
+        <v>350</v>
+      </c>
+      <c r="E40" t="n">
+        <v>350</v>
+      </c>
+      <c r="F40" t="n">
+        <v>350</v>
+      </c>
+      <c r="G40" t="n">
+        <v>350</v>
+      </c>
+      <c r="H40" t="n">
+        <v>350</v>
+      </c>
+      <c r="I40" t="n">
+        <v>350</v>
+      </c>
+      <c r="J40" t="n">
+        <v>350</v>
+      </c>
+      <c r="K40" t="n">
+        <v>350</v>
+      </c>
+      <c r="L40" t="n">
+        <v>350</v>
+      </c>
+      <c r="M40" t="n">
+        <v>350</v>
+      </c>
+      <c r="N40" t="n">
+        <v>350</v>
+      </c>
+      <c r="O40" t="n">
+        <v>350</v>
+      </c>
+      <c r="P40" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>350</v>
+      </c>
+      <c r="R40" t="n">
+        <v>350</v>
+      </c>
+      <c r="S40" t="n">
+        <v>350</v>
+      </c>
+      <c r="T40" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="C40" t="n">
-        <v>350</v>
-      </c>
-      <c r="D40" t="n">
-        <v>350</v>
-      </c>
-      <c r="E40" t="n">
-        <v>350</v>
-      </c>
-      <c r="F40" t="n">
-        <v>350</v>
-      </c>
-      <c r="G40" t="n">
-        <v>350</v>
-      </c>
-      <c r="H40" t="n">
-        <v>350</v>
-      </c>
-      <c r="I40" t="n">
-        <v>350</v>
-      </c>
-      <c r="J40" t="n">
-        <v>350</v>
-      </c>
-      <c r="K40" t="n">
-        <v>350</v>
-      </c>
-      <c r="L40" t="n">
-        <v>350</v>
-      </c>
-      <c r="M40" t="n">
-        <v>350</v>
-      </c>
-      <c r="N40" t="n">
-        <v>350</v>
-      </c>
-      <c r="O40" t="n">
-        <v>350</v>
-      </c>
-      <c r="P40" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>350</v>
-      </c>
-      <c r="R40" t="n">
-        <v>350</v>
-      </c>
-      <c r="S40" t="n">
-        <v>350</v>
-      </c>
-      <c r="T40" t="n">
-        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30608,13 +30608,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I42" t="n">
-        <v>154.4486233659061</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30662,7 +30662,7 @@
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>263.0617733495848</v>
       </c>
     </row>
     <row r="43">
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
@@ -30878,16 +30878,16 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T45" t="n">
         <v>350</v>
       </c>
       <c r="U45" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="V45" t="n">
         <v>350</v>
@@ -30963,10 +30963,10 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="V46" t="n">
         <v>350</v>
@@ -34752,19 +34752,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>369.4444444444444</v>
+        <v>385</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="O2" t="n">
         <v>385</v>
       </c>
       <c r="P2" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="Q2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
@@ -34889,19 +34889,19 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>109.6685269368134</v>
+        <v>7.254996772563674</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34934,13 +34934,13 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>385</v>
+        <v>385.0000000000026</v>
       </c>
       <c r="N5" t="n">
-        <v>385</v>
+        <v>385.0000000000025</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>385.0000000000018</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>369.4444444444376</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35126,22 +35126,22 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>12.42190496730753</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,22 +35165,22 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>-7.855444689792219e-12</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>151.6180515037017</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>385</v>
+        <v>385.0000000000015</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -35226,19 +35226,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>385</v>
+        <v>385.0000000000028</v>
       </c>
       <c r="N8" t="n">
-        <v>385</v>
+        <v>385.0000000000027</v>
       </c>
       <c r="O8" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>369.4444444444374</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,16 +35351,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>53.62826530319553</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -35369,16 +35369,16 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>107.7154453423565</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35411,16 +35411,16 @@
         <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35460,16 +35460,16 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35694,25 +35694,25 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>559</v>
+        <v>536.4141414141418</v>
       </c>
       <c r="M14" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q14" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,7 +35928,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -35937,7 +35937,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>93.38475247205324</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
         <v>559</v>
@@ -35946,10 +35946,10 @@
         <v>559</v>
       </c>
       <c r="P17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36068,7 +36068,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D19" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E19" t="n">
         <v>69.01909516304346</v>
@@ -36122,7 +36122,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V19" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W19" t="n">
         <v>123.6271901612903</v>
@@ -36165,13 +36165,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>93.38475247205329</v>
       </c>
       <c r="K20" t="n">
-        <v>141.1524110730754</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -36180,13 +36180,13 @@
         <v>559</v>
       </c>
       <c r="O20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36302,7 +36302,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C22" t="n">
-        <v>77.27475335195533</v>
+        <v>69.48608398608951</v>
       </c>
       <c r="D22" t="n">
         <v>64.46378194444452</v>
@@ -36365,7 +36365,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X22" t="n">
-        <v>94.76768520402656</v>
+        <v>102.5563545698924</v>
       </c>
       <c r="Y22" t="n">
         <v>62.53464715053764</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N23" t="n">
         <v>559</v>
       </c>
-      <c r="L23" t="n">
-        <v>559.0000000000001</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" t="n">
-        <v>536.4141414141413</v>
+        <v>559</v>
       </c>
       <c r="P23" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36593,10 +36593,10 @@
         <v>139.9754334937423</v>
       </c>
       <c r="U25" t="n">
-        <v>191.2529393596762</v>
+        <v>199.0416087255421</v>
       </c>
       <c r="V25" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W25" t="n">
         <v>123.6271901612903</v>
@@ -36651,13 +36651,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>300.1141042229716</v>
+      </c>
+      <c r="P26" t="n">
         <v>559</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>300.1141042229714</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36876,10 +36876,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -36888,13 +36888,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>136.375834564038</v>
+        <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -37116,25 +37116,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N32" t="n">
         <v>559</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>257.1230221309867</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37301,13 +37301,13 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U34" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V34" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W34" t="n">
         <v>123.6271901612903</v>
@@ -37353,25 +37353,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>516.0089179080152</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="N35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37508,7 +37508,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J37" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K37" t="n">
         <v>61.47922619885696</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37587,7 +37587,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>136.375834564038</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -37602,10 +37602,10 @@
         <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>443.0293889420883</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>55.09753029705556</v>
+        <v>62.88619966292134</v>
       </c>
       <c r="C40" t="n">
         <v>77.27475335195533</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37827,13 +37827,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
         <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -37842,7 +37842,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -38064,7 +38064,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>141.1524110730754</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -38073,16 +38073,16 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>559</v>
+        <v>257.1230221309867</v>
       </c>
       <c r="O44" t="n">
         <v>559</v>
       </c>
       <c r="P44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38249,10 +38249,10 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U46" t="n">
-        <v>191.2529393596762</v>
+        <v>199.0416087255421</v>
       </c>
       <c r="V46" t="n">
         <v>150.8296897837838</v>
